--- a/file/DATA/ปรับรายชื่อคนไข้ Demi .xlsx
+++ b/file/DATA/ปรับรายชื่อคนไข้ Demi .xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ratsapanphuksaritanon/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ratsapanphuksaritanon/Desktop/Tone/Dao/doc/AppBolt/demi-plus-web-v2/file/DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16024B7B-7C13-8D44-84E0-37FA37D42D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CB3495-B840-704E-BAA1-DD26A53762CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="19440" windowHeight="12240" xr2:uid="{493625A2-FE23-49F0-8D72-420B791986D6}"/>
   </bookViews>
